--- a/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 36 D20 Spring 2024 24GE01I54 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 36 D20 Spring 2024 24GE01I54 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ccm243\OneDrive - Cornell University\Desktop\GLNPO Counts\2024\Spring\Erie\d20\Zoops\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A65CFC-9EE6-4653-B38B-CE60643EC0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E39D071-F3E4-41BD-BA71-48E5C50A44C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9B6CD60E-57CD-4BDE-8D54-EEE07B43523C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9B6CD60E-57CD-4BDE-8D54-EEE07B43523C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$142</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1250" r:id="rId2"/>
+    <pivotCache cacheId="9" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -464,7 +464,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -482,7 +482,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3428,7 +3427,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB70CBD1-59A9-437C-AFFA-1CB761969C64}" name="PivotTable1" cacheId="1250" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB70CBD1-59A9-437C-AFFA-1CB761969C64}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T5:W20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -3867,19 +3866,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854BC98D-415C-4B77-B152-DE6C3F475693}">
   <dimension ref="A1:W142"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.1796875" customWidth="1"/>
-    <col min="23" max="23" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.21875" customWidth="1"/>
+    <col min="23" max="23" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3935,7 +3934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -4041,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -4094,7 +4093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4153,7 +4152,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -4218,7 +4217,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4273,17 +4272,17 @@
       <c r="T7" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="U7" s="11">
+      <c r="U7">
         <v>2</v>
       </c>
-      <c r="V7" s="11">
+      <c r="V7">
         <v>14</v>
       </c>
-      <c r="W7" s="11">
+      <c r="W7">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4338,15 +4337,14 @@
       <c r="T8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="U8" s="11">
+      <c r="U8">
         <v>40</v>
       </c>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11">
+      <c r="W8">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -4401,15 +4399,14 @@
       <c r="T9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9">
         <v>44</v>
       </c>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11">
+      <c r="W9">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -4464,17 +4461,17 @@
       <c r="T10" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="U10" s="11">
+      <c r="U10">
         <v>2</v>
       </c>
-      <c r="V10" s="11">
+      <c r="V10">
         <v>2</v>
       </c>
-      <c r="W10" s="11">
+      <c r="W10">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4529,17 +4526,17 @@
       <c r="T11" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="U11" s="11">
+      <c r="U11">
         <v>9</v>
       </c>
-      <c r="V11" s="11">
+      <c r="V11">
         <v>9</v>
       </c>
-      <c r="W11" s="11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -4594,15 +4591,14 @@
       <c r="T12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="U12" s="11">
+      <c r="U12">
         <v>66</v>
       </c>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11">
+      <c r="W12">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -4657,17 +4653,17 @@
       <c r="T13" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="U13" s="11">
+      <c r="U13">
         <v>0</v>
       </c>
-      <c r="V13" s="11">
-        <v>1</v>
-      </c>
-      <c r="W13" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -4722,17 +4718,17 @@
       <c r="T14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="U14" s="11">
+      <c r="U14">
         <v>0</v>
       </c>
-      <c r="V14" s="11">
-        <v>1</v>
-      </c>
-      <c r="W14" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -4787,17 +4783,17 @@
       <c r="T15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="U15" s="11">
+      <c r="U15">
         <v>2</v>
       </c>
-      <c r="V15" s="11">
+      <c r="V15">
         <v>4</v>
       </c>
-      <c r="W15" s="11">
+      <c r="W15">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -4852,17 +4848,17 @@
       <c r="T16" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="U16" s="11">
+      <c r="U16">
         <v>0</v>
       </c>
-      <c r="V16" s="11">
-        <v>1</v>
-      </c>
-      <c r="W16" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -4917,17 +4913,17 @@
       <c r="T17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="U17" s="11">
-        <v>1</v>
-      </c>
-      <c r="V17" s="11">
-        <v>1</v>
-      </c>
-      <c r="W17" s="11">
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -4982,15 +4978,14 @@
       <c r="T18" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="U18" s="11">
+      <c r="U18">
         <v>56</v>
       </c>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11">
+      <c r="W18">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -5045,17 +5040,17 @@
       <c r="T19" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="U19" s="11">
+      <c r="U19">
         <v>0</v>
       </c>
-      <c r="V19" s="11">
-        <v>1</v>
-      </c>
-      <c r="W19" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -5110,17 +5105,17 @@
       <c r="T20" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="U20" s="11">
+      <c r="U20">
         <v>222</v>
       </c>
-      <c r="V20" s="11">
+      <c r="V20">
         <v>34</v>
       </c>
-      <c r="W20" s="11">
+      <c r="W20">
         <v>256</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -5173,7 +5168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -5226,7 +5221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -5278,17 +5273,17 @@
       <c r="Q23">
         <v>1</v>
       </c>
-      <c r="T23" s="12" t="s">
+      <c r="T23" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="U23" s="13" t="s">
+      <c r="U23" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="V23" s="14">
+      <c r="V23" s="13">
         <v>0.995</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -5340,15 +5335,15 @@
       <c r="Q24">
         <v>1</v>
       </c>
-      <c r="T24" s="15"/>
-      <c r="U24" s="13" t="s">
+      <c r="T24" s="14"/>
+      <c r="U24" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="V24" s="14">
+      <c r="V24" s="13">
         <v>0.997</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -5400,17 +5395,17 @@
       <c r="Q25">
         <v>1</v>
       </c>
-      <c r="T25" s="12" t="s">
+      <c r="T25" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="U25" s="13" t="s">
+      <c r="U25" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="V25" s="14">
+      <c r="V25" s="13">
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -5465,15 +5460,15 @@
       <c r="R26" t="s">
         <v>48</v>
       </c>
-      <c r="T26" s="15"/>
-      <c r="U26" s="13" t="s">
+      <c r="T26" s="14"/>
+      <c r="U26" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="V26" s="14">
+      <c r="V26" s="13">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -5525,15 +5520,15 @@
       <c r="Q27">
         <v>1</v>
       </c>
-      <c r="T27" s="16" t="s">
+      <c r="T27" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="U27" s="17" t="s">
+      <c r="U27" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="V27" s="18"/>
-    </row>
-    <row r="28" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+      <c r="V27" s="17"/>
+    </row>
+    <row r="28" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -5585,15 +5580,15 @@
       <c r="Q28">
         <v>1</v>
       </c>
-      <c r="T28" s="16" t="s">
+      <c r="T28" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="U28" s="17" t="s">
+      <c r="U28" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="V28" s="18"/>
-    </row>
-    <row r="29" spans="1:23" ht="16" x14ac:dyDescent="0.4">
+      <c r="V28" s="17"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -5645,15 +5640,15 @@
       <c r="Q29">
         <v>1</v>
       </c>
-      <c r="T29" s="13" t="s">
+      <c r="T29" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="U29" s="17"/>
-      <c r="V29" s="18" t="s">
+      <c r="U29" s="16"/>
+      <c r="V29" s="17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -5706,7 +5701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -5759,7 +5754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -5812,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -5865,7 +5860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -5918,7 +5913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -5971,7 +5966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -6024,7 +6019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -6077,7 +6072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -6130,7 +6125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -6183,7 +6178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -6236,7 +6231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -6289,7 +6284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -6342,7 +6337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -6395,7 +6390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -6448,7 +6443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -6501,7 +6496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -6554,7 +6549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -6607,7 +6602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -6660,7 +6655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -6713,7 +6708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -6766,7 +6761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -6819,7 +6814,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -6872,7 +6867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -6925,7 +6920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -6978,7 +6973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -7031,7 +7026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -7084,7 +7079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -7137,7 +7132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -7190,7 +7185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -7243,7 +7238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -7296,7 +7291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -7349,7 +7344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -7402,7 +7397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -7455,7 +7450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -7508,7 +7503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -7561,7 +7556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -7614,7 +7609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -7667,7 +7662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -7720,7 +7715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -7773,7 +7768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -7826,7 +7821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -7879,7 +7874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -7932,7 +7927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -7985,7 +7980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -8038,7 +8033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -8091,7 +8086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -8144,7 +8139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -8197,7 +8192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -8250,7 +8245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -8303,7 +8298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -8356,7 +8351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -8409,7 +8404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -8462,7 +8457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -8515,7 +8510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -8568,7 +8563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -8621,7 +8616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -8674,7 +8669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -8727,7 +8722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -8780,7 +8775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -8833,7 +8828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -8886,7 +8881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -8939,7 +8934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -8992,7 +8987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -9045,7 +9040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -9098,7 +9093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -9151,7 +9146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -9204,7 +9199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -9257,7 +9252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -9310,7 +9305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -9363,7 +9358,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -9416,7 +9411,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -9469,7 +9464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -9522,7 +9517,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -9575,7 +9570,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -9628,7 +9623,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -9681,7 +9676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -9734,7 +9729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -9787,7 +9782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -9840,7 +9835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -9893,7 +9888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -9946,7 +9941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -9999,7 +9994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -10052,7 +10047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -10105,7 +10100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -10158,7 +10153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -10211,7 +10206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -10264,7 +10259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -10317,7 +10312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -10370,7 +10365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -10423,7 +10418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -10476,7 +10471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -10529,7 +10524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -10582,7 +10577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -10635,7 +10630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -10688,7 +10683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -10741,7 +10736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -10794,7 +10789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -10835,7 +10830,7 @@
         <v>62</v>
       </c>
       <c r="N127" s="4" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="O127">
         <v>0.65400000000000003</v>
@@ -10850,7 +10845,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -10903,7 +10898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -10956,7 +10951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -11009,7 +11004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -11062,7 +11057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -11115,7 +11110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -11168,7 +11163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -11221,7 +11216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -11274,7 +11269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -11327,7 +11322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -11380,7 +11375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -11433,7 +11428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5" t="s">
         <v>18</v>
       </c>
@@ -11474,7 +11469,7 @@
         <v>62</v>
       </c>
       <c r="N139" s="8" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="O139" s="5" t="s">
         <v>35</v>
@@ -11486,7 +11481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="5" t="s">
         <v>18</v>
       </c>
@@ -11539,7 +11534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5" t="s">
         <v>18</v>
       </c>
@@ -11592,7 +11587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="5" t="s">
         <v>18</v>
       </c>
